--- a/du_lieu_test/bo_cong_ty/SO_NHAP.xlsx
+++ b/du_lieu_test/bo_cong_ty/SO_NHAP.xlsx
@@ -21391,112 +21391,116 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Tên CLB và Chỉ tiêu là bắt buộc. Buổi chọn trong danh sách thả xuống</t>
+          <t xml:space="preserve">        Cột "Tên CLB" (tên dự án) và "Chỉ tiêu" (số chỗ) là bắt buộc.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        (chỉ có một buổi thì để trống cả cột).</t>
+          <t xml:space="preserve">        Cột "Buổi" (quý) chọn trong danh sách thả xuống;</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Suất ưu tiên / Cấp bậc: chỉ điền nếu dự án giữ chỗ cho một nhóm</t>
+          <t xml:space="preserve">        chỉ có một quý thì để trống cả cột.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        nhân viên (ví dụ nhóm chinh_sach). Mã CLB để trống, phần mềm tự tạo.</t>
+          <t xml:space="preserve">        Workspace này xếp theo thứ hạng Cấp bậc, nên cột "Suất ưu tiên" và cột Cấp bậc ở sheet này</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        không có tác dụng: cứ để trống. Cột "Mã CLB" (mã dự án) cũng để trống, phần mềm tự tạo.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Bước 2. Sheet "2. Nhân viên": mỗi nhân viên một dòng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Mã HS là bắt buộc và không được trùng.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Cấp bậc: chỉ điền với nhân viên thuộc nhóm đó.</t>
+          <t xml:space="preserve">        Cột "Mã HS" (mã nhân viên) là bắt buộc và không được trùng.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cột Cấp bậc: chỉ điền với nhân viên thuộc nhóm đó.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Bước 3. NV1, NV2, NV3…: chọn tên dự án trong danh sách thả xuống,</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        theo thứ tự thích nhất trước. Không cần điền kín.</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Bước 3. Các cột NV1, NV2, NV3… (NV = nguyện vọng): chọn tên dự án trong danh sách thả xuống,</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Nhiều buổi: cứ điền chung một danh sách — phần mềm tự chia</t>
+          <t xml:space="preserve">        theo thứ tự thích nhất trước. Không cần điền kín.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        theo buổi của từng dự án.</t>
+          <t xml:space="preserve">        Nhiều quý: cứ điền chung một danh sách — phần mềm tự chia</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        theo quý của từng dự án.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Bước 4. Cột "KPI" (đứng sau cột Cấp bậc): KPI của cả người đó, MỘT ô cho cả dòng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Có KPI = đã thi, và KPI ấy áp cho mọi nguyện vọng của dòng. Để trống = không thi.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Thi rồi mà chưa có KPI: gõ chữ  thi  rồi chấm sau trong phần mềm.</t>
+          <t xml:space="preserve">        Có KPI thì KPI ấy áp cho mọi nguyện vọng của dòng. Để trống = chưa có KPI.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Sẽ có KPI nhưng chưa nhập: gõ chữ  thi  rồi nhập KPI sau trong phần mềm.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -21528,14 +21532,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sổ có lỗi (dự án trùng tên, NV ghi tên dự án không có, KPI không phải số…)</t>
+          <t>Sổ có lỗi (dự án trùng tên, NV ghi tên dự án không có, KPI không phải số) thì phần mềm KHÔNG nạp gì cả</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>thì phần mềm KHÔNG nạp gì cả và chỉ rõ sheet, dòng cần sửa.</t>
+          <t>và chỉ rõ sheet, dòng cần sửa.</t>
         </is>
       </c>
     </row>
@@ -21566,14 +21570,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HS001   Nguyễn Văn An   9,5      Tin học      Bóng rổ</t>
+          <t xml:space="preserve">  001   Nguyễn Văn An   9,5      Dự án A    Dự án B</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  → An có KPI 9,5 cho cả hai nguyện vọng: Tin học rồi Bóng rổ.</t>
+          <t xml:space="preserve">  → An có KPI 9,5 cho cả hai nguyện vọng: Dự án A rồi Dự án B.</t>
         </is>
       </c>
     </row>
